--- a/docs/pension_data_combined_2026-07-02.xlsx
+++ b/docs/pension_data_combined_2026-07-02.xlsx
@@ -1203,7 +1203,7 @@
         <v>1.2226</v>
       </c>
       <c r="D46" t="n">
-        <v>59523351</v>
+        <v>59523417</v>
       </c>
     </row>
     <row r="47">
